--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>120.073588259475</v>
+        <v>19.51195809216469</v>
       </c>
       <c r="D2" t="n">
-        <v>4.973026416131042</v>
+        <v>0.8081167926212943</v>
       </c>
       <c r="E2" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F2" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>86.31109503528965</v>
+        <v>14.02555294323457</v>
       </c>
       <c r="D3" t="n">
-        <v>38.82331773560833</v>
+        <v>6.308789132036353</v>
       </c>
       <c r="E3" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F3" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>86.65075867426522</v>
+        <v>14.0807482845681</v>
       </c>
       <c r="D4" t="n">
-        <v>3.352621781772372</v>
+        <v>0.5448010395380105</v>
       </c>
       <c r="E4" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F4" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>82.20536726434318</v>
+        <v>13.35837218045577</v>
       </c>
       <c r="D5" t="n">
-        <v>21.04022505112898</v>
+        <v>3.41903657080846</v>
       </c>
       <c r="E5" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F5" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.49200823501504</v>
+        <v>12.10495133818994</v>
       </c>
       <c r="D6" t="n">
-        <v>2.321398046197343</v>
+        <v>0.3772271825070682</v>
       </c>
       <c r="E6" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F6" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.47889837269038</v>
+        <v>13.07782098556219</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.1625</v>
       </c>
       <c r="E7" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F7" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>89.43816879837458</v>
+        <v>14.53370242973587</v>
       </c>
       <c r="D8" t="n">
-        <v>4.669047011971495</v>
+        <v>0.758720139445368</v>
       </c>
       <c r="E8" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F8" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>72.15805216343755</v>
+        <v>11.7256834765586</v>
       </c>
       <c r="D9" t="n">
-        <v>25.84193405214778</v>
+        <v>4.199314283474015</v>
       </c>
       <c r="E9" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F9" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>74.36368821887352</v>
+        <v>12.08409933556695</v>
       </c>
       <c r="D10" t="n">
-        <v>45.3771493162547</v>
+        <v>7.373786763891389</v>
       </c>
       <c r="E10" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F10" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>71.53641431541504</v>
+        <v>11.62466732625495</v>
       </c>
       <c r="D11" t="n">
-        <v>9.055385138137417</v>
+        <v>1.47150008494733</v>
       </c>
       <c r="E11" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F11" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>57.24466976817895</v>
+        <v>9.302258837329079</v>
       </c>
       <c r="D12" t="n">
-        <v>15.44820488325369</v>
+        <v>2.510333293528725</v>
       </c>
       <c r="E12" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F12" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>58.31518996900037</v>
+        <v>9.476218369962561</v>
       </c>
       <c r="D13" t="n">
-        <v>15.48565644574217</v>
+        <v>2.516419172433102</v>
       </c>
       <c r="E13" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F13" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>87.43101432339874</v>
+        <v>14.2075398275523</v>
       </c>
       <c r="D14" t="n">
-        <v>1.591143222775212</v>
+        <v>0.2585607737009719</v>
       </c>
       <c r="E14" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F14" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.67885347693051</v>
+        <v>10.02281369000121</v>
       </c>
       <c r="D15" t="n">
-        <v>46.60531681638432</v>
+        <v>7.573363982662453</v>
       </c>
       <c r="E15" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F15" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.0461148367888</v>
+        <v>8.944993660978179</v>
       </c>
       <c r="D16" t="n">
-        <v>28.8930018439683</v>
+        <v>4.695112799644849</v>
       </c>
       <c r="E16" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F16" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>54.74062775153387</v>
+        <v>8.895352009624254</v>
       </c>
       <c r="D17" t="n">
-        <v>20.5526490907584</v>
+        <v>3.33980547724824</v>
       </c>
       <c r="E17" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F17" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.68196826932633</v>
+        <v>9.210819843765529</v>
       </c>
       <c r="D18" t="n">
-        <v>16.69440079286009</v>
+        <v>2.712840128839764</v>
       </c>
       <c r="E18" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F18" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>47.06581146612944</v>
+        <v>7.648194363246034</v>
       </c>
       <c r="D19" t="n">
-        <v>27.61856897708399</v>
+        <v>4.488017458776149</v>
       </c>
       <c r="E19" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F19" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>65.03493715037766</v>
+        <v>10.56817728693637</v>
       </c>
       <c r="D20" t="n">
-        <v>13.78092789075964</v>
+        <v>2.239400782248442</v>
       </c>
       <c r="E20" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F20" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>54.78534125556722</v>
+        <v>8.902617954029672</v>
       </c>
       <c r="D21" t="n">
-        <v>13.17753627492984</v>
+        <v>2.1413496446761</v>
       </c>
       <c r="E21" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F21" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>86.08366601172683</v>
+        <v>13.98859572690561</v>
       </c>
       <c r="D22" t="n">
-        <v>6.270219121191736</v>
+        <v>1.018910607193657</v>
       </c>
       <c r="E22" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F22" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>42.56692529453315</v>
+        <v>6.917125360361637</v>
       </c>
       <c r="D23" t="n">
-        <v>19.7229340855705</v>
+        <v>3.204976788905207</v>
       </c>
       <c r="E23" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F23" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>74.19432722724345</v>
+        <v>12.05657817442706</v>
       </c>
       <c r="D24" t="n">
-        <v>13.55716372392081</v>
+        <v>2.203039105137132</v>
       </c>
       <c r="E24" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F24" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>65.54605796748415</v>
+        <v>10.65123441971617</v>
       </c>
       <c r="D25" t="n">
-        <v>63.92012880724543</v>
+        <v>10.38702093117738</v>
       </c>
       <c r="E25" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F25" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>41.46929845348586</v>
+        <v>6.738760998691451</v>
       </c>
       <c r="D26" t="n">
-        <v>3.44988065233555</v>
+        <v>0.5606056060045269</v>
       </c>
       <c r="E26" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F26" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>47.42791226145506</v>
+        <v>7.707035742486447</v>
       </c>
       <c r="D27" t="n">
-        <v>10.64665045828008</v>
+        <v>1.730080699470514</v>
       </c>
       <c r="E27" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F27" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>30.50731856286226</v>
+        <v>4.957439266465117</v>
       </c>
       <c r="D28" t="n">
-        <v>15.98816867673831</v>
+        <v>2.598077409969976</v>
       </c>
       <c r="E28" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F28" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>54.9769071079504</v>
+        <v>8.933747405041942</v>
       </c>
       <c r="D29" t="n">
-        <v>52.39726778134391</v>
+        <v>8.514556014468386</v>
       </c>
       <c r="E29" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F29" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>22.91040766656964</v>
+        <v>3.722941245817566</v>
       </c>
       <c r="D30" t="n">
-        <v>23.15525816732801</v>
+        <v>3.762729452190802</v>
       </c>
       <c r="E30" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F30" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>37.99432188903311</v>
+        <v>6.174077306967881</v>
       </c>
       <c r="D31" t="n">
-        <v>8.695425535306184</v>
+        <v>1.413006649487255</v>
       </c>
       <c r="E31" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F31" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>69.50972709213676</v>
+        <v>11.29533065247222</v>
       </c>
       <c r="D32" t="n">
-        <v>11.42365965879586</v>
+        <v>1.856344694554328</v>
       </c>
       <c r="E32" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F32" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>23.72055491544592</v>
+        <v>3.854590173759962</v>
       </c>
       <c r="D33" t="n">
-        <v>22.38705134598291</v>
+        <v>3.637895843722223</v>
       </c>
       <c r="E33" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F33" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>73.07617084216278</v>
+        <v>11.87487776185145</v>
       </c>
       <c r="D34" t="n">
-        <v>7.006695210852104</v>
+        <v>1.138587971763467</v>
       </c>
       <c r="E34" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F34" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>40.03944043678888</v>
+        <v>6.506409070978193</v>
       </c>
       <c r="D35" t="n">
-        <v>22.33999325064658</v>
+        <v>3.63024890323007</v>
       </c>
       <c r="E35" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F35" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>11.40182758071169</v>
+        <v>1.85279698186565</v>
       </c>
       <c r="D36" t="n">
-        <v>13.65521377990448</v>
+        <v>2.218972239234478</v>
       </c>
       <c r="E36" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F36" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>88.34723279690549</v>
+        <v>14.35642532949714</v>
       </c>
       <c r="D37" t="n">
-        <v>10.26861453383291</v>
+        <v>1.668649861747848</v>
       </c>
       <c r="E37" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F37" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>53.30152969048216</v>
+        <v>8.66149857470335</v>
       </c>
       <c r="D38" t="n">
-        <v>9.133386445608943</v>
+        <v>1.484175297411453</v>
       </c>
       <c r="E38" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F38" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>33.6902057993388</v>
+        <v>5.474658442392555</v>
       </c>
       <c r="D39" t="n">
-        <v>31.54620246476775</v>
+        <v>5.126257900524759</v>
       </c>
       <c r="E39" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F39" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>66.76731021479665</v>
+        <v>10.84968790990446</v>
       </c>
       <c r="D40" t="n">
-        <v>5.609960193819164</v>
+        <v>0.9116185314956142</v>
       </c>
       <c r="E40" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F40" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>19.33878632996706</v>
+        <v>3.142552778619647</v>
       </c>
       <c r="D41" t="n">
-        <v>21.46547762362809</v>
+        <v>3.488140113839564</v>
       </c>
       <c r="E41" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F41" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>27.46522058312719</v>
+        <v>4.463098344758168</v>
       </c>
       <c r="D42" t="n">
-        <v>24.76662806869757</v>
+        <v>4.024577061163355</v>
       </c>
       <c r="E42" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F42" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>29.5583217017339</v>
+        <v>4.803227276531758</v>
       </c>
       <c r="D43" t="n">
-        <v>27.99012115877887</v>
+        <v>4.548394688301566</v>
       </c>
       <c r="E43" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F43" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>28.06328584418198</v>
+        <v>4.560283949679572</v>
       </c>
       <c r="D44" t="n">
-        <v>30.1405505558045</v>
+        <v>4.897839465318231</v>
       </c>
       <c r="E44" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F44" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>40.5332670700739</v>
+        <v>6.586655898887009</v>
       </c>
       <c r="D45" t="n">
-        <v>22.19291104312606</v>
+        <v>3.606348044507985</v>
       </c>
       <c r="E45" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F45" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>88.38884862958656</v>
+        <v>14.36318790230782</v>
       </c>
       <c r="D46" t="n">
-        <v>12.2065556157337</v>
+        <v>1.983565287556727</v>
       </c>
       <c r="E46" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F46" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>13.64217670470024</v>
+        <v>2.216853714513789</v>
       </c>
       <c r="D47" t="n">
-        <v>14.76212783568546</v>
+        <v>2.398845773298888</v>
       </c>
       <c r="E47" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F47" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>14.46278029296735</v>
+        <v>2.350201797607194</v>
       </c>
       <c r="D48" t="n">
-        <v>11.68134537114712</v>
+        <v>1.898218622811407</v>
       </c>
       <c r="E48" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F48" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>35.69313790984641</v>
+        <v>5.800134910350042</v>
       </c>
       <c r="D49" t="n">
-        <v>14.14213562373095</v>
+        <v>2.29809703885628</v>
       </c>
       <c r="E49" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F49" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>19.86953063602403</v>
+        <v>3.228798728353905</v>
       </c>
       <c r="D50" t="n">
-        <v>13.1599544386159</v>
+        <v>2.138492596275084</v>
       </c>
       <c r="E50" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F50" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>35.95154162414712</v>
+        <v>5.842125513923907</v>
       </c>
       <c r="D51" t="n">
-        <v>28.03208941891565</v>
+        <v>4.555214530573793</v>
       </c>
       <c r="E51" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F51" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>77.80636963342377</v>
+        <v>12.64353506543136</v>
       </c>
       <c r="D52" t="n">
-        <v>1.986124708578163</v>
+        <v>0.3227452651439515</v>
       </c>
       <c r="E52" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F52" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>7.956915231419774</v>
+        <v>1.292998725105713</v>
       </c>
       <c r="D53" t="n">
-        <v>4.625750689828018</v>
+        <v>0.7516844870970529</v>
       </c>
       <c r="E53" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F53" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>90.53909501475039</v>
+        <v>14.71260293989694</v>
       </c>
       <c r="D54" t="n">
-        <v>3.704165589759834</v>
+        <v>0.601926908335973</v>
       </c>
       <c r="E54" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F54" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>99.39108397373886</v>
+        <v>16.15105114573257</v>
       </c>
       <c r="D55" t="n">
-        <v>10.41892358014236</v>
+        <v>1.693075081773134</v>
       </c>
       <c r="E55" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F55" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>67.56446010961918</v>
+        <v>10.97922476781312</v>
       </c>
       <c r="D56" t="n">
-        <v>8.459234124630234</v>
+        <v>1.374625545252413</v>
       </c>
       <c r="E56" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F56" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>75.44106422752523</v>
+        <v>12.25917293697285</v>
       </c>
       <c r="D57" t="n">
-        <v>4.47213595499958</v>
+        <v>0.7267220926874317</v>
       </c>
       <c r="E57" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F57" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>29.96878811075413</v>
+        <v>4.869928067997546</v>
       </c>
       <c r="D58" t="n">
-        <v>23.72575970445876</v>
+        <v>3.855435951974548</v>
       </c>
       <c r="E58" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F58" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>88.40624903879922</v>
+        <v>14.36601546880487</v>
       </c>
       <c r="D59" t="n">
-        <v>9.171422072554046</v>
+        <v>1.490356086790033</v>
       </c>
       <c r="E59" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F59" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>3.448029558737141</v>
+        <v>0.5603048032947855</v>
       </c>
       <c r="D60" t="n">
-        <v>12.27443169982704</v>
+        <v>1.994595151221894</v>
       </c>
       <c r="E60" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F60" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>67.43108099767235</v>
+        <v>10.95755066212176</v>
       </c>
       <c r="D61" t="n">
-        <v>8.864102551842844</v>
+        <v>1.440416664674462</v>
       </c>
       <c r="E61" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F61" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>94.28370939300926</v>
+        <v>15.32110277636401</v>
       </c>
       <c r="D62" t="n">
-        <v>4.743416490252569</v>
+        <v>0.7708051796660425</v>
       </c>
       <c r="E62" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F62" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>10.35147174811314</v>
+        <v>1.682114159068386</v>
       </c>
       <c r="D63" t="n">
-        <v>18.34558975483505</v>
+        <v>2.981158335160696</v>
       </c>
       <c r="E63" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F63" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>76.78131440405174</v>
+        <v>12.47696359065841</v>
       </c>
       <c r="D64" t="n">
-        <v>12.15296031608943</v>
+        <v>1.974856051364532</v>
       </c>
       <c r="E64" t="n">
-        <v>26.89388730011998</v>
+        <v>4.370256686269497</v>
       </c>
       <c r="F64" t="n">
-        <v>12.70374204849822</v>
+        <v>2.06435808288096</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
